--- a/Analisis Cajas JockeyPlaza.xlsx
+++ b/Analisis Cajas JockeyPlaza.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eparedes\Documents\SPSA\00_Analisis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\SP44812227\Documents\00_Analisis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{392B3260-91D4-4546-B0F0-A221586FAD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{35DB002B-B957-45E3-A45C-9EF763EDF92B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="30940" windowHeight="16780"/>
   </bookViews>
   <sheets>
-    <sheet name="Analisis Cajas JockeyPlaza" sheetId="1" r:id="rId1"/>
+    <sheet name="Productividad" sheetId="1" r:id="rId1"/>
+    <sheet name="Velocidad" sheetId="2" r:id="rId2"/>
+    <sheet name="P&amp;L" sheetId="5" r:id="rId3"/>
+    <sheet name="Dotacion" sheetId="4" r:id="rId4"/>
+    <sheet name="Horas Extra" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
   <si>
     <t>Mes</t>
   </si>
@@ -31,21 +37,9 @@
     <t>Prod</t>
   </si>
   <si>
-    <t xml:space="preserve"> Vta </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Vta AA </t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
-    <t xml:space="preserve"> JEq </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JEqAA </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Prod </t>
   </si>
   <si>
@@ -206,13 +200,161 @@
   </si>
   <si>
     <t>preguntar como amarrar productividad y 6 curvas</t>
+  </si>
+  <si>
+    <t>Vta</t>
+  </si>
+  <si>
+    <t>Vta AA</t>
+  </si>
+  <si>
+    <t>Jeq</t>
+  </si>
+  <si>
+    <t>Jeq AA</t>
+  </si>
+  <si>
+    <t>velocidad</t>
+  </si>
+  <si>
+    <t>predic venta</t>
+  </si>
+  <si>
+    <t>azure</t>
+  </si>
+  <si>
+    <t>gasto/venta P&amp;L</t>
+  </si>
+  <si>
+    <t>horas extra</t>
+  </si>
+  <si>
+    <t>Meta Promedio</t>
+  </si>
+  <si>
+    <t>Unid x Minuto</t>
+  </si>
+  <si>
+    <t>Unid x Minuto AA</t>
+  </si>
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>enero</t>
+  </si>
+  <si>
+    <t>febrero</t>
+  </si>
+  <si>
+    <t>marzo</t>
+  </si>
+  <si>
+    <t>abril</t>
+  </si>
+  <si>
+    <t>mayo</t>
+  </si>
+  <si>
+    <t>junio</t>
+  </si>
+  <si>
+    <t>julio</t>
+  </si>
+  <si>
+    <t>agosto</t>
+  </si>
+  <si>
+    <t>septiembre</t>
+  </si>
+  <si>
+    <t>octubre</t>
+  </si>
+  <si>
+    <t>noviembre</t>
+  </si>
+  <si>
+    <t>diciembre</t>
+  </si>
+  <si>
+    <t>Delivea</t>
+  </si>
+  <si>
+    <t>Lineal</t>
+  </si>
+  <si>
+    <t>Rapida</t>
+  </si>
+  <si>
+    <t>delivea</t>
+  </si>
+  <si>
+    <t>lineal</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>TIENDAS</t>
+  </si>
+  <si>
+    <t>HHE DEL PERIODO</t>
+  </si>
+  <si>
+    <t>COMPENSACION DEL PERIODO</t>
+  </si>
+  <si>
+    <t>HORAS A PAGAR EFECTIVO</t>
+  </si>
+  <si>
+    <t>ENERO</t>
+  </si>
+  <si>
+    <t>ALMACÉN</t>
+  </si>
+  <si>
+    <t>ALMACÉN FRESCOS</t>
+  </si>
+  <si>
+    <t>CAJAS</t>
+  </si>
+  <si>
+    <t>CONTROL DE INVENTARIOS</t>
+  </si>
+  <si>
+    <t>ELECTRO</t>
+  </si>
+  <si>
+    <t>RECEPCIÓN</t>
+  </si>
+  <si>
+    <t>RECEPCIÓN E INVENTARIOS</t>
+  </si>
+  <si>
+    <t>SALA</t>
+  </si>
+  <si>
+    <t>SALA FRESCOS</t>
+  </si>
+  <si>
+    <t>FEBRERO</t>
+  </si>
+  <si>
+    <t>MARZO</t>
+  </si>
+  <si>
+    <t>Total general</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,8 +489,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -528,8 +690,32 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -644,8 +830,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -688,13 +907,71 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="36" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="35" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="34" borderId="12" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="35" borderId="12" xfId="42" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="44">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -727,9 +1004,11 @@
     <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Millares" xfId="42" builtinId="3"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Porcentaje" xfId="43" builtinId="5"/>
     <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
@@ -749,6 +1028,3166 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE"/>
+              <a:t>Velocidad</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'[1]Evolutivo de unidades por minut'!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>9.65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.94</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D56D-4629-9BD8-B91880A442DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'[1]Evolutivo de unidades por minut'!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>11.86</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.87</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.78</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.66</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.74</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.53</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.98</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10.39</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.210000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D56D-4629-9BD8-B91880A442DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="553391264"/>
+        <c:axId val="553387104"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="553391264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553387104"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="553387104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553391264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE"/>
+              <a:t>Velocidad</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'[1]Evolutivo de unidades por minut'!$B$20:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>6.77</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B293-490C-9C81-559121B5D6FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'[1]Evolutivo de unidades por minut'!$C$20:$C$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>11.35</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.9499999999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.67</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.68</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.78</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.46</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.39</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B293-490C-9C81-559121B5D6FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="553391264"/>
+        <c:axId val="553387104"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="553391264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553387104"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="553387104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553391264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-PE"/>
+              <a:t>Velocidad</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'[1]Evolutivo de unidades por minut'!$B$37:$B$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>10.23</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.89</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.26</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.31</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D69B-4237-85A2-E884D1ACD4E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'[1]Evolutivo de unidades por minut'!$C$37:$C$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>11.79</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.09</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.85</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.28</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10.89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.58</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.01</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D69B-4237-85A2-E884D1ACD4E2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="553391264"/>
+        <c:axId val="553387104"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="553391264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553387104"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="553387104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553391264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Evolutivo de unidades por minut"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>9.65</v>
+          </cell>
+          <cell r="C2">
+            <v>11.86</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>10.24</v>
+          </cell>
+          <cell r="C3">
+            <v>11.87</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4">
+            <v>11.55</v>
+          </cell>
+          <cell r="C4">
+            <v>12.41</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>11.95</v>
+          </cell>
+          <cell r="C5">
+            <v>11.78</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6">
+            <v>11.94</v>
+          </cell>
+          <cell r="C6">
+            <v>11.66</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>11.01</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>10.74</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>10.53</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>9.98</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>10.39</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>10.210000000000001</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>9.75</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>6.77</v>
+          </cell>
+          <cell r="C20">
+            <v>11.35</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>7.11</v>
+          </cell>
+          <cell r="C21">
+            <v>9.75</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>9.3000000000000007</v>
+          </cell>
+          <cell r="C22">
+            <v>10.64</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>9</v>
+          </cell>
+          <cell r="C23">
+            <v>9.9499999999999993</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>9.99</v>
+          </cell>
+          <cell r="C24">
+            <v>9.67</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25">
+            <v>8.66</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="C26">
+            <v>8.35</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="C27">
+            <v>7.68</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="C28">
+            <v>6.78</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29">
+            <v>7.09</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30">
+            <v>7.46</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31">
+            <v>7.39</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37">
+            <v>10.23</v>
+          </cell>
+          <cell r="C37">
+            <v>11.79</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38">
+            <v>10.85</v>
+          </cell>
+          <cell r="C38">
+            <v>11.94</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39">
+            <v>11.89</v>
+          </cell>
+          <cell r="C39">
+            <v>12.45</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40">
+            <v>12.26</v>
+          </cell>
+          <cell r="C40">
+            <v>11.76</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41">
+            <v>12.31</v>
+          </cell>
+          <cell r="C41">
+            <v>11.78</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42">
+            <v>11.09</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>10.96</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>10.85</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>10.28</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>10.89</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="C47">
+            <v>10.58</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="C48">
+            <v>10.01</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1047,11 +4486,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D96E2C1-A5BB-4B0B-9569-E1648967906B}">
-  <dimension ref="A1:Y17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1061,61 +4504,61 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="O1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="S1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="T1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="U1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
-        <v>5</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="V1" t="s">
         <v>10</v>
       </c>
-      <c r="S1" t="s">
+      <c r="W1" t="s">
         <v>11</v>
       </c>
-      <c r="T1" t="s">
+      <c r="X1" t="s">
         <v>12</v>
       </c>
-      <c r="U1" t="s">
+      <c r="Y1" t="s">
         <v>13</v>
       </c>
-      <c r="V1" t="s">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>14</v>
-      </c>
-      <c r="W1" t="s">
-        <v>15</v>
-      </c>
-      <c r="X1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>18</v>
       </c>
       <c r="B2">
         <v>209782</v>
@@ -1123,64 +4566,72 @@
       <c r="C2">
         <v>176665</v>
       </c>
-      <c r="E2" s="1">
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="16">
         <v>4650464</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="16">
         <v>4897588</v>
       </c>
-      <c r="G2" s="2">
-        <v>-5.0500000000000003E-2</v>
-      </c>
-      <c r="I2">
+      <c r="G2" s="17">
+        <f>+E2/F2-1</f>
+        <v>-5.0458307232049693E-2</v>
+      </c>
+      <c r="I2" s="23">
         <v>26.3</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="23">
         <v>23.4</v>
       </c>
-      <c r="K2" s="2">
-        <v>0.12720000000000001</v>
-      </c>
-      <c r="M2" s="1">
-        <v>176689</v>
-      </c>
-      <c r="N2" s="1">
-        <v>209747</v>
-      </c>
-      <c r="O2" s="2">
-        <v>-0.15759999999999999</v>
+      <c r="K2" s="17">
+        <f>+I2/J2-1</f>
+        <v>0.12393162393162394</v>
+      </c>
+      <c r="M2" s="16">
+        <f>+E2/I2</f>
+        <v>176823.72623574143</v>
+      </c>
+      <c r="N2" s="16">
+        <f>+F2/J2</f>
+        <v>209298.6324786325</v>
+      </c>
+      <c r="O2" s="17">
+        <f>+M2/N2-1</f>
+        <v>-0.15516062316463752</v>
       </c>
       <c r="P2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="14">
+        <v>4768784</v>
+      </c>
+      <c r="S2" s="14">
+        <v>205063.6428</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" t="s">
         <v>19</v>
       </c>
-      <c r="R2">
-        <v>4768784</v>
-      </c>
-      <c r="S2">
-        <v>205063.6428</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="X2" t="s">
         <v>20</v>
-      </c>
-      <c r="U2" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X2" t="s">
-        <v>24</v>
       </c>
       <c r="Y2">
         <v>-118319.765</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>190228</v>
@@ -1188,64 +4639,72 @@
       <c r="C3">
         <v>182761</v>
       </c>
-      <c r="E3" s="1">
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="16">
         <v>4642034</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="16">
         <v>4649018</v>
       </c>
-      <c r="G3" s="2">
-        <v>-1.5E-3</v>
-      </c>
-      <c r="I3">
+      <c r="G3" s="17">
+        <f t="shared" ref="G3:G14" si="0">+E3/F3-1</f>
+        <v>-1.5022527338031111E-3</v>
+      </c>
+      <c r="I3" s="23">
         <v>25.4</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="23">
         <v>24.4</v>
       </c>
-      <c r="K3" s="2">
-        <v>3.9300000000000002E-2</v>
-      </c>
-      <c r="M3" s="1">
-        <v>182757</v>
-      </c>
-      <c r="N3" s="1">
-        <v>190222</v>
-      </c>
-      <c r="O3" s="2">
-        <v>-3.9199999999999999E-2</v>
+      <c r="K3" s="17">
+        <f t="shared" ref="K3:K13" si="1">+I3/J3-1</f>
+        <v>4.0983606557376984E-2</v>
+      </c>
+      <c r="M3" s="16">
+        <f t="shared" ref="M3:N13" si="2">+E3/I3</f>
+        <v>182757.24409448821</v>
+      </c>
+      <c r="N3" s="16">
+        <f t="shared" si="2"/>
+        <v>190533.52459016396</v>
+      </c>
+      <c r="O3" s="17">
+        <f t="shared" ref="O3:O13" si="3">+M3/N3-1</f>
+        <v>-4.0813187665543205E-2</v>
       </c>
       <c r="P3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R3">
+        <v>15</v>
+      </c>
+      <c r="R3" s="14">
         <v>4535561</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="14">
         <v>195034.77710000001</v>
       </c>
-      <c r="T3" t="s">
-        <v>26</v>
+      <c r="T3" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="U3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="V3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="W3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="X3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y3">
         <v>106472.71030000001</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>247480</v>
@@ -1253,64 +4712,72 @@
       <c r="C4">
         <v>205656</v>
       </c>
-      <c r="E4" s="1">
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="16">
         <v>5140864</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="16">
         <v>5722544</v>
       </c>
-      <c r="G4" s="2">
-        <v>-0.1016</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="18">
+        <f t="shared" si="0"/>
+        <v>-0.1016470996116412</v>
+      </c>
+      <c r="I4" s="23">
         <v>25</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="23">
         <v>23.1</v>
       </c>
-      <c r="K4" s="2">
-        <v>8.1299999999999997E-2</v>
-      </c>
-      <c r="M4" s="1">
-        <v>205635</v>
-      </c>
-      <c r="N4" s="1">
-        <v>247515</v>
-      </c>
-      <c r="O4" s="2">
-        <v>-0.16919999999999999</v>
+      <c r="K4" s="17">
+        <f t="shared" si="1"/>
+        <v>8.2251082251082241E-2</v>
+      </c>
+      <c r="M4" s="16">
+        <f t="shared" si="2"/>
+        <v>205634.56</v>
+      </c>
+      <c r="N4" s="16">
+        <f t="shared" si="2"/>
+        <v>247729.17748917747</v>
+      </c>
+      <c r="O4" s="17">
+        <f t="shared" si="3"/>
+        <v>-0.16992192004115647</v>
       </c>
       <c r="P4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="14">
+        <v>5884601</v>
+      </c>
+      <c r="S4" s="14">
+        <v>253045.17050000001</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W4" t="s">
         <v>31</v>
       </c>
-      <c r="R4">
-        <v>5884601</v>
-      </c>
-      <c r="S4">
-        <v>253045.17050000001</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="X4" t="s">
         <v>32</v>
-      </c>
-      <c r="U4" t="s">
-        <v>33</v>
-      </c>
-      <c r="V4" t="s">
-        <v>34</v>
-      </c>
-      <c r="W4" t="s">
-        <v>35</v>
-      </c>
-      <c r="X4" t="s">
-        <v>36</v>
       </c>
       <c r="Y4">
         <v>-743736.89780000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>221937</v>
@@ -1318,64 +4785,72 @@
       <c r="C5">
         <v>222979</v>
       </c>
-      <c r="E5" s="1">
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="16">
         <v>4771432</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="16">
         <v>4815149</v>
       </c>
-      <c r="G5" s="2">
-        <v>-9.1000000000000004E-3</v>
-      </c>
-      <c r="I5">
+      <c r="G5" s="17">
+        <f t="shared" si="0"/>
+        <v>-9.0790544591662359E-3</v>
+      </c>
+      <c r="I5" s="24">
         <v>21.4</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="23">
         <v>21.7</v>
       </c>
-      <c r="K5" s="2">
-        <v>-1.38E-2</v>
-      </c>
-      <c r="M5" s="1">
-        <v>222964</v>
-      </c>
-      <c r="N5" s="1">
-        <v>221896</v>
-      </c>
-      <c r="O5" s="2">
-        <v>4.7999999999999996E-3</v>
+      <c r="K5" s="17">
+        <f t="shared" si="1"/>
+        <v>-1.3824884792626779E-2</v>
+      </c>
+      <c r="M5" s="16">
+        <f t="shared" si="2"/>
+        <v>222964.11214953274</v>
+      </c>
+      <c r="N5" s="16">
+        <f t="shared" si="2"/>
+        <v>221896.267281106</v>
+      </c>
+      <c r="O5" s="17">
+        <f t="shared" si="3"/>
+        <v>4.8123606652379358E-3</v>
       </c>
       <c r="P5" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5">
+        <v>27</v>
+      </c>
+      <c r="R5" s="14">
         <v>4985433</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="14">
         <v>214379.79870000001</v>
       </c>
-      <c r="T5" t="s">
-        <v>38</v>
+      <c r="T5" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="U5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="V5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="W5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="X5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y5">
         <v>-214000.31270000001</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>219436</v>
@@ -1383,448 +4858,1695 @@
       <c r="C6">
         <v>240159</v>
       </c>
-      <c r="E6" s="1">
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="16">
         <v>5098630</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="16">
         <v>5087648</v>
       </c>
-      <c r="G6" s="2">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="I6">
+      <c r="G6" s="17">
+        <f t="shared" si="0"/>
+        <v>2.1585612841139579E-3</v>
+      </c>
+      <c r="I6" s="24">
         <v>21.2</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="23">
         <v>23.2</v>
       </c>
-      <c r="K6" s="2">
-        <v>-8.4500000000000006E-2</v>
-      </c>
-      <c r="M6" s="1">
-        <v>240162</v>
-      </c>
-      <c r="N6" s="1">
-        <v>219390</v>
-      </c>
-      <c r="O6" s="2">
-        <v>9.4700000000000006E-2</v>
+      <c r="K6" s="17">
+        <f t="shared" si="1"/>
+        <v>-8.6206896551724088E-2</v>
+      </c>
+      <c r="M6" s="16">
+        <f t="shared" si="2"/>
+        <v>240501.41509433964</v>
+      </c>
+      <c r="N6" s="16">
+        <f t="shared" si="2"/>
+        <v>219295.1724137931</v>
+      </c>
+      <c r="O6" s="17">
+        <f t="shared" si="3"/>
+        <v>9.6701821782615438E-2</v>
       </c>
       <c r="P6" t="s">
-        <v>43</v>
-      </c>
-      <c r="R6">
+        <v>39</v>
+      </c>
+      <c r="R6" s="14">
         <v>5255854</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="14">
         <v>226008.23250000001</v>
       </c>
-      <c r="T6" t="s">
-        <v>44</v>
+      <c r="T6" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="U6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="V6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="W6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y6">
         <v>-157223.9038</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>206054</v>
       </c>
-      <c r="E7" s="1">
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="19">
         <v>4959493</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="16">
         <v>4776174</v>
       </c>
-      <c r="G7" s="2">
-        <v>3.8399999999999997E-2</v>
-      </c>
-      <c r="I7">
+      <c r="G7" s="20">
+        <f t="shared" si="0"/>
+        <v>3.8381976871026957E-2</v>
+      </c>
+      <c r="I7" s="25">
         <v>24.1</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="23">
         <v>23.2</v>
       </c>
-      <c r="K7" s="2">
-        <v>3.8399999999999997E-2</v>
-      </c>
-      <c r="M7" s="1">
-        <v>206045</v>
-      </c>
-      <c r="N7" s="1">
-        <v>206047</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="K7" s="20">
+        <f t="shared" si="1"/>
+        <v>3.8793103448276023E-2</v>
+      </c>
+      <c r="M7" s="19">
+        <f>+N7</f>
+        <v>205869.56896551725</v>
+      </c>
+      <c r="N7" s="16">
+        <f t="shared" si="2"/>
+        <v>205869.56896551725</v>
+      </c>
+      <c r="O7" s="20">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="14">
         <v>4959493</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="14">
         <v>213264.36600000001</v>
       </c>
-      <c r="T7" t="s">
-        <v>33</v>
+      <c r="T7" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="X7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y7">
         <v>-4959493.0870000003</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>204658</v>
       </c>
-      <c r="E8" s="1">
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="19">
         <v>4906031</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="16">
         <v>4761073</v>
       </c>
-      <c r="G8" s="2">
-        <v>3.04E-2</v>
-      </c>
-      <c r="I8">
+      <c r="G8" s="20">
+        <f t="shared" si="0"/>
+        <v>3.0446498089821361E-2</v>
+      </c>
+      <c r="I8" s="25">
         <v>24</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="23">
         <v>23.3</v>
       </c>
-      <c r="K8" s="2">
-        <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="M8" s="1">
-        <v>204674</v>
-      </c>
-      <c r="N8" s="1">
-        <v>204689</v>
-      </c>
-      <c r="O8" s="2">
-        <v>-1E-4</v>
-      </c>
-      <c r="R8">
+      <c r="K8" s="20">
+        <f t="shared" si="1"/>
+        <v>3.0042918454935563E-2</v>
+      </c>
+      <c r="M8" s="19">
+        <f t="shared" ref="M8:M13" si="4">+N8</f>
+        <v>204337.89699570814</v>
+      </c>
+      <c r="N8" s="16">
+        <f t="shared" si="2"/>
+        <v>204337.89699570814</v>
+      </c>
+      <c r="O8" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="14">
         <v>4906031</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="14">
         <v>210965.4235</v>
       </c>
-      <c r="T8" t="s">
-        <v>49</v>
+      <c r="T8" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="X8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y8">
         <v>-4906030.852</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>217708</v>
       </c>
-      <c r="E9" s="1">
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="19">
         <v>4950561</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="16">
         <v>4795344</v>
       </c>
-      <c r="G9" s="2">
-        <v>3.2399999999999998E-2</v>
-      </c>
-      <c r="I9">
+      <c r="G9" s="20">
+        <f t="shared" si="0"/>
+        <v>3.2368272224057248E-2</v>
+      </c>
+      <c r="I9" s="25">
         <v>22.7</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="23">
         <v>22</v>
       </c>
-      <c r="K9" s="2">
-        <v>3.2199999999999999E-2</v>
-      </c>
-      <c r="M9" s="1">
-        <v>217703</v>
-      </c>
-      <c r="N9" s="1">
-        <v>217673</v>
-      </c>
-      <c r="O9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="R9">
+      <c r="K9" s="20">
+        <f t="shared" si="1"/>
+        <v>3.1818181818181746E-2</v>
+      </c>
+      <c r="M9" s="19">
+        <f t="shared" si="4"/>
+        <v>217970.18181818182</v>
+      </c>
+      <c r="N9" s="16">
+        <f t="shared" si="2"/>
+        <v>217970.18181818182</v>
+      </c>
+      <c r="O9" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="14">
         <v>4950561</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="14">
         <v>212880.25570000001</v>
       </c>
-      <c r="T9" t="s">
-        <v>51</v>
+      <c r="T9" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="X9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y9">
         <v>-4950560.5470000003</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>189586</v>
       </c>
-      <c r="E10" s="1">
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="19">
         <v>4592727</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="16">
         <v>4351276</v>
       </c>
-      <c r="G10" s="2">
-        <v>5.5500000000000001E-2</v>
-      </c>
-      <c r="I10">
+      <c r="G10" s="20">
+        <f t="shared" si="0"/>
+        <v>5.5489700032818057E-2</v>
+      </c>
+      <c r="I10" s="25">
         <v>24.2</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="23">
         <v>23</v>
       </c>
-      <c r="K10" s="2">
-        <v>5.5800000000000002E-2</v>
-      </c>
-      <c r="M10" s="1">
-        <v>189547</v>
-      </c>
-      <c r="N10" s="1">
-        <v>189598</v>
-      </c>
-      <c r="O10" s="2">
-        <v>-2.9999999999999997E-4</v>
-      </c>
-      <c r="R10">
+      <c r="K10" s="20">
+        <f t="shared" si="1"/>
+        <v>5.2173913043478182E-2</v>
+      </c>
+      <c r="M10" s="19">
+        <f t="shared" si="4"/>
+        <v>189185.91304347827</v>
+      </c>
+      <c r="N10" s="16">
+        <f t="shared" si="2"/>
+        <v>189185.91304347827</v>
+      </c>
+      <c r="O10" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="14">
         <v>4592727</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="14">
         <v>197492.98850000001</v>
       </c>
-      <c r="T10" t="s">
-        <v>26</v>
+      <c r="T10" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="X10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Y10">
         <v>-4592727.4649999999</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B11">
         <v>196429</v>
       </c>
-      <c r="E11" s="1">
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="19">
         <v>4684317</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="16">
         <v>4440124</v>
       </c>
-      <c r="G11" s="2">
-        <v>5.5E-2</v>
-      </c>
-      <c r="I11">
+      <c r="G11" s="20">
+        <f t="shared" si="0"/>
+        <v>5.499688747431386E-2</v>
+      </c>
+      <c r="I11" s="25">
         <v>23.9</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="23">
         <v>22.6</v>
       </c>
-      <c r="K11" s="2">
-        <v>5.5300000000000002E-2</v>
-      </c>
-      <c r="M11" s="1">
-        <v>196407</v>
-      </c>
-      <c r="N11" s="1">
-        <v>196466</v>
-      </c>
-      <c r="O11" s="2">
-        <v>-2.9999999999999997E-4</v>
-      </c>
-      <c r="R11">
+      <c r="K11" s="20">
+        <f t="shared" si="1"/>
+        <v>5.7522123893805288E-2</v>
+      </c>
+      <c r="M11" s="19">
+        <f t="shared" si="4"/>
+        <v>196465.66371681416</v>
+      </c>
+      <c r="N11" s="16">
+        <f t="shared" si="2"/>
+        <v>196465.66371681416</v>
+      </c>
+      <c r="O11" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="14">
         <v>4684317</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="14">
         <v>201431.4406</v>
       </c>
-      <c r="T11" t="s">
-        <v>55</v>
+      <c r="T11" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="X11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Y11">
         <v>-4684316.727</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <v>194585</v>
       </c>
-      <c r="E12" s="1">
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="19">
         <v>4878777</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="16">
         <v>4884966</v>
       </c>
-      <c r="G12" s="2">
-        <v>-1.2999999999999999E-3</v>
-      </c>
-      <c r="I12">
+      <c r="G12" s="20">
+        <f t="shared" si="0"/>
+        <v>-1.2669484291190081E-3</v>
+      </c>
+      <c r="I12" s="25">
         <v>25.1</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="23">
         <v>25.1</v>
       </c>
-      <c r="K12" s="2">
-        <v>-1.1999999999999999E-3</v>
-      </c>
-      <c r="M12" s="1">
-        <v>194606</v>
-      </c>
-      <c r="N12" s="1">
-        <v>194620</v>
-      </c>
-      <c r="O12" s="2">
-        <v>-1E-4</v>
-      </c>
-      <c r="R12">
+      <c r="K12" s="20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="19">
+        <f t="shared" si="4"/>
+        <v>194620.15936254978</v>
+      </c>
+      <c r="N12" s="16">
+        <f t="shared" si="2"/>
+        <v>194620.15936254978</v>
+      </c>
+      <c r="O12" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="14">
         <v>4878777</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="14">
         <v>209793.47029999999</v>
       </c>
-      <c r="T12" t="s">
-        <v>57</v>
+      <c r="T12" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="X12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y12">
         <v>-4878776.915</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B13">
         <v>242755</v>
       </c>
-      <c r="E13" s="1">
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="19">
         <v>7340846</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="16">
         <v>7203511</v>
       </c>
-      <c r="G13" s="2">
-        <v>1.9099999999999999E-2</v>
-      </c>
-      <c r="I13">
+      <c r="G13" s="20">
+        <f t="shared" si="0"/>
+        <v>1.9065008715888787E-2</v>
+      </c>
+      <c r="I13" s="25">
         <v>30.2</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="23">
         <v>29.7</v>
       </c>
-      <c r="K13" s="2">
-        <v>1.9199999999999998E-2</v>
-      </c>
-      <c r="M13" s="1">
-        <v>242753</v>
-      </c>
-      <c r="N13" s="1">
-        <v>242788</v>
-      </c>
-      <c r="O13" s="2">
-        <v>-1E-4</v>
-      </c>
-      <c r="R13">
+      <c r="K13" s="20">
+        <f t="shared" si="1"/>
+        <v>1.6835016835016869E-2</v>
+      </c>
+      <c r="M13" s="19">
+        <f t="shared" si="4"/>
+        <v>242542.45791245793</v>
+      </c>
+      <c r="N13" s="16">
+        <f t="shared" si="2"/>
+        <v>242542.45791245793</v>
+      </c>
+      <c r="O13" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="14">
         <v>7340846</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="14">
         <v>315665.50579999998</v>
       </c>
-      <c r="T13" t="s">
-        <v>59</v>
+      <c r="T13" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="X13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="Y13">
         <v>-7340846.1189999999</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="E14" s="1">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="E14" s="21">
+        <f>SUM(E2:E13)</f>
         <v>60616176</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="21">
+        <f>SUM(F2:F13)</f>
         <v>60384415</v>
       </c>
-      <c r="G14" s="2">
-        <v>3.8E-3</v>
-      </c>
-      <c r="I14">
-        <v>294</v>
-      </c>
-      <c r="J14">
-        <v>285</v>
-      </c>
-      <c r="K14" s="2">
-        <v>3.1600000000000003E-2</v>
-      </c>
-      <c r="M14" s="1">
-        <v>206177</v>
-      </c>
-      <c r="N14" s="1">
-        <v>211875</v>
-      </c>
-      <c r="O14" s="2">
-        <v>-2.69E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="G14" s="22">
+        <f t="shared" si="0"/>
+        <v>3.8380929913786055E-3</v>
+      </c>
+      <c r="I14" s="26">
+        <f>SUM(I2:I13)</f>
+        <v>293.5</v>
+      </c>
+      <c r="J14" s="26">
+        <f>SUM(J2:J13)</f>
+        <v>284.7</v>
+      </c>
+      <c r="K14" s="22">
+        <f>+I14/J14-1</f>
+        <v>3.0909729539866593E-2</v>
+      </c>
+      <c r="M14" s="21">
+        <f>SUM(M2:M13)</f>
+        <v>2479672.8993888097</v>
+      </c>
+      <c r="N14" s="21">
+        <f>SUM(N2:N13)</f>
+        <v>2539744.6160675804</v>
+      </c>
+      <c r="O14" s="22">
+        <f t="shared" ref="O14" si="5">+M14/N14-1</f>
+        <v>-2.365266031030433E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="I16">
         <v>2.8</v>
       </c>
     </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I17" t="s">
-        <v>61</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="9:10" x14ac:dyDescent="0.35">
+      <c r="I19" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="9:10" x14ac:dyDescent="0.35">
+      <c r="I20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="9:10" x14ac:dyDescent="0.35">
+      <c r="I21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="9:10" x14ac:dyDescent="0.35">
+      <c r="I22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>9.65</v>
+      </c>
+      <c r="C2">
+        <v>11.86</v>
+      </c>
+      <c r="D2">
+        <v>2026</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>10.24</v>
+      </c>
+      <c r="C3">
+        <v>11.87</v>
+      </c>
+      <c r="D3">
+        <v>2026</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>11.55</v>
+      </c>
+      <c r="C4">
+        <v>12.41</v>
+      </c>
+      <c r="D4">
+        <v>2026</v>
+      </c>
+      <c r="E4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>11.95</v>
+      </c>
+      <c r="C5">
+        <v>11.78</v>
+      </c>
+      <c r="D5">
+        <v>2026</v>
+      </c>
+      <c r="E5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>11.94</v>
+      </c>
+      <c r="C6">
+        <v>11.66</v>
+      </c>
+      <c r="D6">
+        <v>2026</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>11.01</v>
+      </c>
+      <c r="D7">
+        <v>2026</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>10.74</v>
+      </c>
+      <c r="D8">
+        <v>2026</v>
+      </c>
+      <c r="E8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>10.53</v>
+      </c>
+      <c r="D9">
+        <v>2026</v>
+      </c>
+      <c r="E9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>9.98</v>
+      </c>
+      <c r="D10">
+        <v>2026</v>
+      </c>
+      <c r="E10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>10.39</v>
+      </c>
+      <c r="D11">
+        <v>2026</v>
+      </c>
+      <c r="E11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>10.210000000000001</v>
+      </c>
+      <c r="D12">
+        <v>2026</v>
+      </c>
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>9.75</v>
+      </c>
+      <c r="D13">
+        <v>2026</v>
+      </c>
+      <c r="E13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="14">
+        <v>13</v>
+      </c>
+      <c r="B20" s="14">
+        <v>6.77</v>
+      </c>
+      <c r="C20" s="14">
+        <v>11.35</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="14">
+        <v>13</v>
+      </c>
+      <c r="B21" s="14">
+        <v>7.11</v>
+      </c>
+      <c r="C21" s="14">
+        <v>9.75</v>
+      </c>
+      <c r="D21" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="14">
+        <v>13</v>
+      </c>
+      <c r="B22" s="14">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="C22" s="14">
+        <v>10.64</v>
+      </c>
+      <c r="D22" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="14">
+        <v>13</v>
+      </c>
+      <c r="B23" s="14">
+        <v>9</v>
+      </c>
+      <c r="C23" s="14">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="14">
+        <v>13</v>
+      </c>
+      <c r="B24" s="14">
+        <v>9.99</v>
+      </c>
+      <c r="C24" s="14">
+        <v>9.67</v>
+      </c>
+      <c r="D24" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="14">
+        <v>13</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14">
+        <v>8.66</v>
+      </c>
+      <c r="D25" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="14">
+        <v>13</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14">
+        <v>8.35</v>
+      </c>
+      <c r="D26" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="14">
+        <v>13</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14">
+        <v>7.68</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="14">
+        <v>13</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="14">
+        <v>13</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14">
+        <v>7.09</v>
+      </c>
+      <c r="D29" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="14">
+        <v>13</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14">
+        <v>7.46</v>
+      </c>
+      <c r="D30" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="14">
+        <v>13</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14">
+        <v>7.39</v>
+      </c>
+      <c r="D31" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="14">
+        <v>13</v>
+      </c>
+      <c r="B37" s="14">
+        <v>10.23</v>
+      </c>
+      <c r="C37" s="14">
+        <v>11.79</v>
+      </c>
+      <c r="D37" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="14">
+        <v>13</v>
+      </c>
+      <c r="B38" s="14">
+        <v>10.85</v>
+      </c>
+      <c r="C38" s="14">
+        <v>11.94</v>
+      </c>
+      <c r="D38" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="14">
+        <v>13</v>
+      </c>
+      <c r="B39" s="14">
+        <v>11.89</v>
+      </c>
+      <c r="C39" s="14">
+        <v>12.45</v>
+      </c>
+      <c r="D39" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="14">
+        <v>13</v>
+      </c>
+      <c r="B40" s="14">
+        <v>12.26</v>
+      </c>
+      <c r="C40" s="14">
+        <v>11.76</v>
+      </c>
+      <c r="D40" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="14">
+        <v>13</v>
+      </c>
+      <c r="B41" s="14">
+        <v>12.31</v>
+      </c>
+      <c r="C41" s="14">
+        <v>11.78</v>
+      </c>
+      <c r="D41" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="14">
+        <v>13</v>
+      </c>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14">
+        <v>11.09</v>
+      </c>
+      <c r="D42" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="14">
+        <v>13</v>
+      </c>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14">
+        <v>10.96</v>
+      </c>
+      <c r="D43" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="14">
+        <v>13</v>
+      </c>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14">
+        <v>10.85</v>
+      </c>
+      <c r="D44" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="14">
+        <v>13</v>
+      </c>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14">
+        <v>10.28</v>
+      </c>
+      <c r="D45" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="14">
+        <v>13</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14">
+        <v>10.89</v>
+      </c>
+      <c r="D46" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="14">
+        <v>13</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14">
+        <v>10.58</v>
+      </c>
+      <c r="D47" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="14">
+        <v>13</v>
+      </c>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14">
+        <v>10.01</v>
+      </c>
+      <c r="D48" s="14">
+        <v>2026</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C2:F36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:6" ht="39" x14ac:dyDescent="0.35">
+      <c r="C2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="4">
+        <v>128.06666666666666</v>
+      </c>
+      <c r="E3" s="4">
+        <v>96.533333333333346</v>
+      </c>
+      <c r="F3" s="4">
+        <v>106.14999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="6">
+        <v>31.366666666666667</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>14.166666666666664</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.48333333333333339</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.73333333333333328</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C6" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E6" s="11">
+        <v>42.083333333333336</v>
+      </c>
+      <c r="F6" s="11">
+        <v>4.9333333333333336</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="6">
+        <v>16.783333333333331</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1.5333333333333332</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C10" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="6">
+        <v>40.916666666666671</v>
+      </c>
+      <c r="E11" s="6">
+        <v>52</v>
+      </c>
+      <c r="F11" s="6">
+        <v>61.816666666666663</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="6">
+        <v>34.983333333333334</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F12" s="6">
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="4">
+        <v>144.61666666666667</v>
+      </c>
+      <c r="E14" s="4">
+        <v>54.716666666666669</v>
+      </c>
+      <c r="F14" s="4">
+        <v>56.133333333333326</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C15" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="6">
+        <v>23.383333333333333</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>31.366666666666667</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0.48333333333333339</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C17" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="13">
+        <v>3.2833333333333332</v>
+      </c>
+      <c r="E17" s="13">
+        <v>3.3666666666666671</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0.18333333333333332</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="6">
+        <v>8.1499999999999986</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="6">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="6">
+        <v>3.4666666666666668</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <v>1.5333333333333332</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C21" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.11666666666666667</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C22" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="6">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="E22" s="6">
+        <v>14</v>
+      </c>
+      <c r="F22" s="6">
+        <v>9.5833333333333321</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C23" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" s="6">
+        <v>33.966666666666669</v>
+      </c>
+      <c r="E23" s="6">
+        <v>36.85</v>
+      </c>
+      <c r="F23" s="6">
+        <v>7.2833333333333332</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C24" s="7"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C25" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="4">
+        <v>154.6</v>
+      </c>
+      <c r="E25" s="4">
+        <v>39.483333333333334</v>
+      </c>
+      <c r="F25" s="4">
+        <v>61.416666666666671</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C26" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="6">
+        <v>22.433333333333337</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <v>23.383333333333333</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C28" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="13">
+        <v>9.1333333333333329</v>
+      </c>
+      <c r="E28" s="13">
+        <v>4.9833333333333334</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0.28333333333333333</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C30" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="6">
+        <v>17.516666666666666</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <v>3.4666666666666668</v>
+      </c>
+    </row>
+    <row r="32" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C32" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0.11666666666666667</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C33" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="6">
+        <v>53.733333333333334</v>
+      </c>
+      <c r="E33" s="6">
+        <v>25</v>
+      </c>
+      <c r="F33" s="6">
+        <v>25.833333333333336</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="6">
+        <v>49.18333333333333</v>
+      </c>
+      <c r="E34" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="F34" s="6">
+        <v>8.1833333333333336</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C35" s="7"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C36" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="9">
+        <v>427.28333333333336</v>
+      </c>
+      <c r="E36" s="9">
+        <v>190.73333333333332</v>
+      </c>
+      <c r="F36" s="9">
+        <v>223.7</v>
       </c>
     </row>
   </sheetData>

--- a/Analisis Cajas JockeyPlaza.xlsx
+++ b/Analisis Cajas JockeyPlaza.xlsx
@@ -6552,4 +6552,265 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010018451F55413CCE40B32872F2EE2F7B17" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="969693e52f69943e32048b02ca88382a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8574a8e8-5383-43f9-82c2-17454492c82a" xmlns:ns3="d25c0998-d329-4608-bd73-3e8a880c0119" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="069909415eb877d2dc8b3adebaeaef02" ns2:_="" ns3:_="">
+    <xsd:import namespace="8574a8e8-5383-43f9-82c2-17454492c82a"/>
+    <xsd:import namespace="d25c0998-d329-4608-bd73-3e8a880c0119"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8574a8e8-5383-43f9-82c2-17454492c82a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9ecfcf50-3ae4-46b1-98e5-a512559b6c25" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="16" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d25c0998-d329-4608-bd73-3e8a880c0119" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{674349b7-f6f9-4818-9607-755bdfad0d86}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d25c0998-d329-4608-bd73-3e8a880c0119">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d25c0998-d329-4608-bd73-3e8a880c0119" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8574a8e8-5383-43f9-82c2-17454492c82a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D3E8208-C40E-402A-82FF-935E765ECF66}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2CFB400-B8A2-4A37-AD3D-36C6DB0E2756}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B289B29-2D2A-4ED6-B655-6C911BF09F62}"/>
 </file>